--- a/03-BOM/Christo-BOM.xlsx
+++ b/03-BOM/Christo-BOM.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arizonastateu-my.sharepoint.com/personal/cjomonjo_sundevils_asu_edu/Documents/3 Junior/Semester 5/EGR 304/Github websites/chvisto.github.io/docs/03-BOM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{451BBD89-C88B-4865-9D93-12CEEE02F764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F96E6546-9EB5-422D-9C7A-03DC1F86577C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43ABA504-260A-4C91-9DF9-3D1E1108C59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
   <si>
     <t>Part Name/Description</t>
   </si>
@@ -58,9 +71,6 @@
     <t>Tactile Switch SPST-NO Top Actuated Through Hole</t>
   </si>
   <si>
-    <t>Red Diffused LED 2V T-1 3/4 Through Hole</t>
-  </si>
-  <si>
     <t>Texas Instruments</t>
   </si>
   <si>
@@ -70,9 +80,6 @@
     <t>Omron Electronics Inc.</t>
   </si>
   <si>
-    <t>Kingbright</t>
-  </si>
-  <si>
     <t>LM7805CT/NOPB</t>
   </si>
   <si>
@@ -82,9 +89,6 @@
     <t>B3F-1000</t>
   </si>
   <si>
-    <t>WP7113ID</t>
-  </si>
-  <si>
     <t>DigiKey</t>
   </si>
   <si>
@@ -97,9 +101,6 @@
     <t>SW400-ND</t>
   </si>
   <si>
-    <t>754-1264-ND</t>
-  </si>
-  <si>
     <t>https://www.ti.com/lit/ds/symlink/lm7805.pdf</t>
   </si>
   <si>
@@ -125,13 +126,132 @@
   </si>
   <si>
     <t>SW1</t>
+  </si>
+  <si>
+    <t>PIC18F47Q10 Curiosity Nano Evaluation Kit (provided in class)</t>
+  </si>
+  <si>
+    <t>Microchip Technology</t>
+  </si>
+  <si>
+    <t>https://ww1.microchip.com/downloads/en/DeviceDoc/PIC18F27-47-57Q43-Data-Sheet-40002147F.pdf</t>
+  </si>
+  <si>
+    <t>CJJ_PIC18F57Q43_CuriosityNano1</t>
+  </si>
+  <si>
+    <t>Microchip Direct</t>
+  </si>
+  <si>
+    <t>0.33 µF Multilayer Ceramic Capacitor</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>K104K10X7RF5UH5</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/vishay-beyschlag-draloric-bc-components/K104K10X7RF5UH5/2356879</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>DM164150</t>
+  </si>
+  <si>
+    <t>General Stock</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t>0.1 µF Ceramic Capacitor</t>
+  </si>
+  <si>
+    <t>In Class Checkoff</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/mxuteuk-Multilayer-Monolithic-Capacitor-10uf-106/dp/B08BFDTK9H/ref=sr_1_12_sspa?crid=NSU2PNH0R78&amp;dchild=1&amp;keywords=10uf%2Bcapacitor&amp;qid=1596815719&amp;sprefix=10uf%2B%2Caps%2C259&amp;sr=8-12-spons&amp;spLa=ZW5jcnlwdGVkUXVhbGlmaWVyPUExVUFONEFXM0RaSVpQJmVuY3J5cHRlZElkPUEwMjIwMTkwOVc3WjdOMFpCTDZOJmVuY3J5cHRlZEFkSWQ9QTA4NjEwNTFNQlNETEJDU1pMMFkmd2lkZ2V0TmFtZT1zcF9tdGYmYWN0aW9uPWNsaWNrUmVkaXJlY3QmZG9Ob3RMb2dDbGljaz10cnVl&amp;th=1</t>
+  </si>
+  <si>
+    <t>DM182029-ND</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>‎GMA_500mA_5x</t>
+  </si>
+  <si>
+    <t>Witonics</t>
+  </si>
+  <si>
+    <t>Fast-Blow Fuse, 500 mA, 5x20mm</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Pack-500mA-250v-Fuses-5x20mm/dp/B00Y7NL78U</t>
+  </si>
+  <si>
+    <t>Fuse holder</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/~/media/electronics/datasheets/fuse_blocks/littelfuse_fuse_block_354_datasheet.pdf.pdf</t>
+  </si>
+  <si>
+    <t>PJ-102AH CONN PWR JACK 2X5.5MM SOLDER</t>
+  </si>
+  <si>
+    <t>LED Red</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cui-devices/PJ-102AH/408448</t>
+  </si>
+  <si>
+    <t>40 Pin (40 X 1) Header Connector</t>
+  </si>
+  <si>
+    <t>40 Pin 2.54mm Single Row Straight Female PCB Header Connector Strip</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Qunqi-2-54mm-Straight-Connector-Arduino/dp/B07CGGSDWF/ref=sr_1_17?dchild=1&amp;keywords=female+header+strips&amp;qid=1595380282&amp;sr=8-17</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Header-Lystaii-Pin-Connector-Electronic/dp/B06ZZN8L9S/ref=sr_1_15?dchild=1&amp;keywords=40+pin+header+male+to+male&amp;qid=1608606507&amp;sr=8-15</t>
+  </si>
+  <si>
+    <t>J2,J3,J4</t>
+  </si>
+  <si>
+    <t>Resistor kit</t>
+  </si>
+  <si>
+    <t>In class checkoffs</t>
+  </si>
+  <si>
+    <t>R1,R2,R3</t>
+  </si>
+  <si>
+    <t>J2,J3,J4,T1,T2,T3,T4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +272,33 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1111"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -200,7 +347,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -211,8 +358,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -519,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="53.46484375" customWidth="1"/>
@@ -528,13 +699,13 @@
     <col min="4" max="4" width="15.53125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="24.19921875" customWidth="1"/>
-    <col min="7" max="7" width="10.46484375" customWidth="1"/>
-    <col min="8" max="8" width="21.1328125" customWidth="1"/>
-    <col min="9" max="9" width="58.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.06640625" customWidth="1"/>
+    <col min="8" max="8" width="38.1328125" customWidth="1"/>
+    <col min="9" max="9" width="152.9296875" customWidth="1"/>
     <col min="10" max="10" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,136 +734,445 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>1.8</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="5">
         <v>1.8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="J2" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="5">
         <v>2.2000000000000002</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="H3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="J3" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>0.24</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>0.24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.21</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.21</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>7.99</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.97360000000000002</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.97360000000000002</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="9">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A14" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -700,8 +1180,15 @@
     <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{82EAE91A-77CB-4B01-B7CB-0FE0F66D6F48}"/>
+    <hyperlink ref="I8" r:id="rId6" xr:uid="{19FF755A-3480-40C9-8847-0383F3B3D7D1}"/>
+    <hyperlink ref="I7" r:id="rId7" xr:uid="{39359D98-F163-41F6-B83D-7826DD33029C}"/>
+    <hyperlink ref="I10" r:id="rId8" xr:uid="{B9AD4884-7C29-41C6-A5D8-5A67F76C4AEB}"/>
+    <hyperlink ref="I11" r:id="rId9" xr:uid="{D331B94A-BE1D-4582-993B-845AF9A0FC16}"/>
+    <hyperlink ref="I12" r:id="rId10" xr:uid="{70BD4BD7-3E66-46AA-8196-98FB3CCF868A}"/>
+    <hyperlink ref="I13" r:id="rId11" xr:uid="{AA3A8FFD-629A-439C-AA31-C6A1155FD51A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>